--- a/test_outputs/invoice_output.xlsx
+++ b/test_outputs/invoice_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lilly Pulitzer dress Size 2</t>
+          <t>Valentine's Day Roses Area Rugs Floor Mat Non-slip Romantic Bedroom Carpet Decor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>5,00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -481,12 +481,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>45,00</t>
+          <t>11,92</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>180,00</t>
+          <t>59,60</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>198,00</t>
+          <t>65,56</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Women Sexy Lingerie Lace Dress Underwear Babydoll Sleepwear G-string Bikini Lot</t>
+          <t>Bohemian Rag Rug- Woven Chindi Dari Living Room Rug/ Hand-Woven Carpet Rug-Mats</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>23,39</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>93,56</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>102,92</t>
         </is>
       </c>
     </row>
@@ -550,12 +550,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Socialite White Black Striped A Line Dress With Pockets Large</t>
+          <t>Hippie 3D Starry Sky Carpet Child Play Area Rug Kids Room Carpets Mat Home Decor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>5,00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10,00</t>
+          <t>11,69</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40,00</t>
+          <t>58,45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>44,00</t>
+          <t>64,29</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rebecca Minkoff Black Polyester Fringe and Lambskin Dress Sz</t>
+          <t>6'8 x 5'Handwoven Afghan Kilim Wool Area Rug Kelim Tapis Oriental Carpet#4434</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -607,12 +607,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9,99</t>
+          <t>259,00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29,97</t>
+          <t>777,00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -622,23 +622,135 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>32,97</t>
+          <t>854,70</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Modern Tribal Geometric 4X6 Indo Gabbeh Wool &amp; Bamboo Silk Oriental Rug Carpet</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2,00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>183,77</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>367,54</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>404,29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pretty Woman Small Large Long Floor Carpet Area Rugs Various Size Soft Rug</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5,00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>36,30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>181,50</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>199,65</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>New Candy Color Soft Anti-Skid Carpet Soft Non slip Rug Living Bedroom Floor Mat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>11,99</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>11,99</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>13,19</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
